--- a/Planilla_Asistencia_UAGRM_2026.xlsx
+++ b/Planilla_Asistencia_UAGRM_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Desktop\CURSOR\propuesta para presusupuesto\control-mantenimiento-vehicular\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC2A3CE-EB33-43A0-8AC9-579739D4BA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEDD080-7792-430C-9519-06B91CEB6F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>UAGRM</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>FIRMA Y SELLO DEL DECANO DE LA FACULTAD</t>
-  </si>
-  <si>
-    <t>Página 1 de 1</t>
   </si>
   <si>
     <t>DPTO. DESARROLLO HUMANO - U.A.G.R.M.</t>
@@ -169,16 +166,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -188,37 +185,37 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -581,7 +578,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -592,17 +589,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -616,8 +613,8 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="7"/>
@@ -628,18 +625,20 @@
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -650,9 +649,7 @@
       <c r="H6" s="11"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>4</v>
-      </c>
+      <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -662,172 +659,161 @@
       <c r="H7" s="11"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H10" s="14" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+    </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="20" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="19" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="F20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+    </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="F21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+      <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F20:H20"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A8:H8"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="1.1811023622047245" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup scale="93" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
